--- a/Result/profitability/6244.xlsx
+++ b/Result/profitability/6244.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2125</v>
+        <v>0.2475</v>
       </c>
       <c r="N2" t="n">
-        <v>16.39</v>
+        <v>17.13375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.51</v>
+        <v>0.54125</v>
       </c>
       <c r="N3" t="n">
-        <v>16.17125</v>
+        <v>16.76125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.67</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9575</v>
+        <v>0.97875</v>
       </c>
       <c r="N4" t="n">
-        <v>15.9725</v>
+        <v>16.3325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.04</v>
       </c>
       <c r="M5" t="n">
-        <v>1.19125</v>
+        <v>1.2325</v>
       </c>
       <c r="N5" t="n">
-        <v>15.00125</v>
+        <v>15.83375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.215</v>
+        <v>1.24625</v>
       </c>
       <c r="N6" t="n">
-        <v>13.50375</v>
+        <v>14.335</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.84</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09875</v>
+        <v>1.15875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.47625</v>
+        <v>12.48125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0425</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.94375</v>
+        <v>10.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6244</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>911</v>
+      </c>
+      <c r="D75" t="n">
+        <v>709</v>
+      </c>
+      <c r="E75" t="n">
+        <v>201</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>98</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>46</v>
+      </c>
+      <c r="J75" t="n">
+        <v>143</v>
+      </c>
+      <c r="K75" t="n">
+        <v>132</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09249999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.07125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3239520958083832</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>33</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4310679611650485</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
